--- a/Vrushali_MyDashboard.xlsx
+++ b/Vrushali_MyDashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\4SN22AI062VAP\StayEase-Data-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E8A8EB-99CB-40DD-86E1-6BC6F3B0C3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DBD64B-74D2-4B95-A849-AA291DC392BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB338318-A5D2-47EA-943F-A9B019A7FA92}"/>
   </bookViews>
